--- a/draftTAPPs/STEM_TAPP_draft_v2.xlsx
+++ b/draftTAPPs/STEM_TAPP_draft_v2.xlsx
@@ -814,12 +814,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>2023-12-07</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Maizey</t>
+          <t>Maizey; Beau</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>2023-12-07</t>
         </is>
       </c>
     </row>

--- a/draftTAPPs/STEM_TAPP_draft_v2.xlsx
+++ b/draftTAPPs/STEM_TAPP_draft_v2.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -658,12 +658,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Claude assisted</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Claude assisted</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7. STEM Acquisition</t>
+          <t>Procedure Author Description</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>How this draft was produced.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Text (free)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2602,43 +2622,23 @@
       <c r="I49" t="inlineStr">
         <is>
           <t>(none)</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Draft generated by Claude (Anthropic) under human review, from analysis of ADA metadata records and the instrumentMetadata exports attached to them. Parameter values and tier assignments are derived, not authored by the laboratory.</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Draft generated by Claude (Anthropic) under human review, from analysis of ADA metadata records and the instrumentMetadata exports attached to them. Parameter values and tier assignments are derived, not authored by the laboratory.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Accelerating Voltage</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Electron beam accelerating voltage.</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Read-Only</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Number + unit</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>200 kV</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Seeded 2026-10-07 from the 25 UAZ instrumentMetadata exports (HyperSpy, .dm4). Constant across all 25. Not recorded by this laboratory: all 78 LBNL exports are .ser files carrying only image dimensions.</t>
+          <t>7. STEM Acquisition</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2649,53 +2649,43 @@
       <c r="I50" t="inlineStr">
         <is>
           <t>(none)</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>200 kV</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>N</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Magnification</t>
+          <t>Accelerating Voltage</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nominal magnification.</t>
+          <t>Electron beam accelerating voltage.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Read-Only</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Number + unit</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2200 to 26000 (21 distinct)</t>
+          <t>200 kV</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Seeded 2026-10-07 from the 25 UAZ instrumentMetadata exports (HyperSpy, .dm4). Not recorded by this laboratory: all 78 LBNL exports are .ser files carrying only image dimensions.</t>
+          <t>Seeded 2026-10-07 from the 25 UAZ instrumentMetadata exports (HyperSpy, .dm4). Constant across all 25. Not recorded by this laboratory: all 78 LBNL exports are .ser files carrying only image dimensions.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2710,7 +2700,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>200 kV</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -2722,12 +2712,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dwell Time per Probe Position</t>
+          <t>Magnification</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dwell time per scanned probe position.</t>
+          <t>Nominal magnification.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2742,17 +2732,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2e-06 to 4e-06 s</t>
+          <t>2200 to 26000 (21 distinct)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Units inconsistent in source: one file records 8.11, which is not seconds. Seeded 2026-10-07 from the 25 UAZ instrumentMetadata exports (HyperSpy, .dm4). Not recorded by this laboratory: all 78 LBNL exports are .ser files carrying only image dimensions.</t>
+          <t>Seeded 2026-10-07 from the 25 UAZ instrumentMetadata exports (HyperSpy, .dm4). Not recorded by this laboratory: all 78 LBNL exports are .ser files carrying only image dimensions.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2767,7 +2757,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>4e-06 s</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -2779,12 +2769,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Camera Length</t>
+          <t>Dwell Time per Probe Position</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Camera length.</t>
+          <t>Dwell time per scanned probe position.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2804,12 +2794,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25 to 37 mm</t>
+          <t>2e-06 to 4e-06 s</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Recorded as 0.0 where not set. Seeded 2026-10-07 from the 25 UAZ instrumentMetadata exports (HyperSpy, .dm4). Not recorded by this laboratory: all 78 LBNL exports are .ser files carrying only image dimensions.</t>
+          <t>Units inconsistent in source: one file records 8.11, which is not seconds. Seeded 2026-10-07 from the 25 UAZ instrumentMetadata exports (HyperSpy, .dm4). Not recorded by this laboratory: all 78 LBNL exports are .ser files carrying only image dimensions.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2824,7 +2814,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>37 mm</t>
+          <t>4e-06 s</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -2836,12 +2826,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Stage X Position</t>
+          <t>Camera Length</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Stage X position.</t>
+          <t>Camera length.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2856,17 +2846,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Number + unit</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>23 distinct values</t>
+          <t>25 to 37 mm</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Seeded 2026-10-07 from the 25 UAZ instrumentMetadata exports (HyperSpy, .dm4). Not recorded by this laboratory: all 78 LBNL exports are .ser files carrying only image dimensions.</t>
+          <t>Recorded as 0.0 where not set. Seeded 2026-10-07 from the 25 UAZ instrumentMetadata exports (HyperSpy, .dm4). Not recorded by this laboratory: all 78 LBNL exports are .ser files carrying only image dimensions.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2881,7 +2871,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-0.1375</t>
+          <t>37 mm</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -2893,12 +2883,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Stage Y Position</t>
+          <t>Stage X Position</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Stage Y position.</t>
+          <t>Stage X position.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2918,7 +2908,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>22 distinct values</t>
+          <t>23 distinct values</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2938,7 +2928,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-0.1776</t>
+          <t>-0.1375</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -2950,12 +2940,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Stage Tilt Alpha</t>
+          <t>Stage Y Position</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Primary stage tilt.</t>
+          <t>Stage Y position.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2970,12 +2960,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.0 to 0.7 deg</t>
+          <t>22 distinct values</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2995,7 +2985,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0.0 deg</t>
+          <t>-0.1776</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3007,12 +2997,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Stage Tilt Beta</t>
+          <t>Stage Tilt Alpha</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Secondary stage tilt.</t>
+          <t>Primary stage tilt.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3032,7 +3022,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-2.9 to 0.1 deg</t>
+          <t>0.0 to 0.7 deg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3052,7 +3042,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0.1 deg</t>
+          <t>0.0 deg</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3064,12 +3054,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Image Pixel Size</t>
+          <t>Stage Tilt Beta</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Physical size of one image pixel.</t>
+          <t>Secondary stage tilt.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3089,12 +3079,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.3696 nm</t>
+          <t>-2.9 to 0.1 deg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Recorded by BOTH laboratories (100% coverage) but in mixed units: m, nm and um all appear and must be normalised before comparison.</t>
+          <t>Seeded 2026-10-07 from the 25 UAZ instrumentMetadata exports (HyperSpy, .dm4). Not recorded by this laboratory: all 78 LBNL exports are .ser files carrying only image dimensions.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3109,24 +3099,24 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0.3696 nm</t>
+          <t>0.1 deg</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2.2766e-10 m</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Image Width</t>
+          <t>Image Pixel Size</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Image width in pixels.</t>
+          <t>Physical size of one image pixel.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3141,17 +3131,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Number + unit</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2048 (also 1024, 4096)</t>
+          <t>0.3696 nm</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Split from a single Image Dimensions item 2026-10-07: the source states it as "2048 x 2048", but the record carries width and height as two properties, so one workbook item could not map to both. Recorded by both laboratories (100% coverage).</t>
+          <t>Recorded by BOTH laboratories (100% coverage) but in mixed units: m, nm and um all appear and must be normalised before comparison.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3166,67 +3156,124 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>0.3696 nm</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2.2766e-10 m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>Image Width</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Image width in pixels.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2048 (also 1024, 4096)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Split from a single Image Dimensions item 2026-10-07: the source states it as "2048 x 2048", but the record carries width and height as two properties, so one workbook item could not map to both. Recorded by both laboratories (100% coverage).</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>Image Height</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Image height in pixels.</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>2048 (also 1024, 4096)</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Split from a single Image Dimensions item 2026-10-07; see Image Width. Recorded by both laboratories (100% coverage).</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t>2048</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>2048</t>
         </is>

--- a/draftTAPPs/STEM_TAPP_draft_v2.xlsx
+++ b/draftTAPPs/STEM_TAPP_draft_v2.xlsx
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>How this draft was produced.</t>
+          <t>Provenance of this TAPP definition: how the definition itself came to be, as distinct from the method it describes. Use it to state that the definition was transcribed from a published protocol, derived from existing metadata records rather than authored by the laboratory, or produced automatically and reviewed by a person. Optional -- a laboratory-authored TAPP needs nothing here. Recorded on schema:creator.schema:description.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">

--- a/draftTAPPs/STEM_TAPP_draft_v2.xlsx
+++ b/draftTAPPs/STEM_TAPP_draft_v2.xlsx
@@ -2675,7 +2675,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Numeric (kV)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Numeric</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Numeric (s)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Numeric (mm)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Numeric</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Numeric</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Numeric (deg)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Numeric (deg)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Number + unit</t>
+          <t>Numeric (nm)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Integer (QuantitativeValue)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Integer (QuantitativeValue)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
